--- a/tsp_results.xlsx
+++ b/tsp_results.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Raw_Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Statistics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Statistical_Test" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Conclusion" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,11 +660,11 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>200.6418</v>
+        <v>192.5553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>207.3561</v>
+        <v>203.5522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -696,11 +696,11 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>192.9081</v>
+        <v>198.1805</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -714,11 +714,11 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>203.5522</v>
+        <v>198.5912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -732,11 +732,11 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>201.7276</v>
+        <v>204.2231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -750,11 +750,11 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>210.5731</v>
+        <v>192.5553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -768,11 +768,11 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>198.1361</v>
+        <v>215.4902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Sài Gòn Mansion-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -786,11 +786,11 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>197.1703</v>
+        <v>192.5553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -804,11 +804,11 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>201.0073</v>
+        <v>206.4804</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -822,11 +822,11 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>262.0404</v>
+        <v>260.8398999999999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Sài Gòn Mansion-&gt;BV Phục hồi chức năng-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -840,11 +840,11 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>300.5769</v>
+        <v>224.7089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;UEH Cơ sở N-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Chợ Bình Tây-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;AEMON Tân Phú-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -858,11 +858,11 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>252.7946</v>
+        <v>242.7831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Vincom Plaza Quang Trung-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Chợ Bình Tây-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -876,11 +876,11 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>241.9738</v>
+        <v>283.9088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -894,11 +894,11 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>241.5202</v>
+        <v>227.5023999999999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Bà Chiểu-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -912,11 +912,11 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>261.1124</v>
+        <v>257.1992999999999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;AEMON Tân Phú-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;UEH Cơ sở B-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;Chợ Bình Tây-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bình Tây-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Lovera Park Khang Điền-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -930,11 +930,11 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>284.4248</v>
+        <v>231.7861999999999</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Sài Gòn Mansion-&gt;BV Phục hồi chức năng-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vincom Plaza Quang Trung-&gt;BV Phục hồi chức năng-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -948,11 +948,11 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>231.5435</v>
+        <v>238.1223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;AEMON Tân Phú-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -966,11 +966,11 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>253.0937</v>
+        <v>248.4392999999999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu di tích Láng Le Bàu Cò-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Chợ Bình Tây-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;UEH Cơ sở B-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;Chợ Bà Chiểu-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -984,11 +984,11 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>259.5384</v>
+        <v>287.4814999999999</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;AEMON Tân Phú-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ Bình Tây-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1002,11 +1002,11 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>208.2586</v>
+        <v>206.2975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1020,11 +1020,11 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>204.7289</v>
+        <v>207.4906</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Bà Chiểu-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1038,11 +1038,11 @@
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>198.2962</v>
+        <v>201.0126</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1056,11 +1056,11 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>197.2742</v>
+        <v>206.0996</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1074,11 +1074,11 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>210.6702</v>
+        <v>207.255</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1092,11 +1092,11 @@
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>206.6334</v>
+        <v>202.8928999999999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1110,11 +1110,11 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>195.9078</v>
+        <v>207.6749</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1128,11 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>209.045</v>
+        <v>200.4226</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1146,11 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>205.0992</v>
+        <v>196.3503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1164,11 +1164,11 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>205.9686</v>
+        <v>198.5151</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Best</t>
+          <t>p_value</t>
         </is>
       </c>
     </row>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>201.41874</v>
+        <v>200.52983</v>
       </c>
       <c r="C2" t="n">
-        <v>5.009134500800622</v>
+        <v>7.321172730595964</v>
       </c>
       <c r="D2" t="n">
-        <v>25.0914284471111</v>
+        <v>53.59957015122197</v>
       </c>
       <c r="E2" t="n">
-        <v>192.9081</v>
+        <v>0.8724377287882789</v>
       </c>
     </row>
     <row r="3">
@@ -1239,16 +1239,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>204.18821</v>
+        <v>203.40111</v>
       </c>
       <c r="C3" t="n">
-        <v>5.201796433808015</v>
+        <v>4.135676694447954</v>
       </c>
       <c r="D3" t="n">
-        <v>27.05868613877779</v>
+        <v>17.10382172099996</v>
       </c>
       <c r="E3" t="n">
-        <v>195.9078</v>
+        <v>0.7826092549174236</v>
       </c>
     </row>
     <row r="4">
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>258.86187</v>
+        <v>250.2771699999999</v>
       </c>
       <c r="C4" t="n">
-        <v>20.579250784713</v>
+        <v>22.10167948093288</v>
       </c>
       <c r="D4" t="n">
-        <v>423.5055628601106</v>
+        <v>488.4842358778894</v>
       </c>
       <c r="E4" t="n">
-        <v>231.5435</v>
+        <v>0.1066776016185869</v>
       </c>
     </row>
     <row r="5">
@@ -1280,13 +1280,13 @@
         <v>237.7336</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1e-12</v>
       </c>
       <c r="E5" t="n">
-        <v>237.7336</v>
+        <v>0.2382754146757105</v>
       </c>
     </row>
   </sheetData>
@@ -1300,49 +1300,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Best Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Best Algorithm (Stat)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
+          <t>p_value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ANOVA (p-value)</t>
+          <t>2-opt</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.532604391192135e-14</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2-opt</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Thống kê có sự khác biệt</t>
-        </is>
+        <v>0.8724377287882789</v>
       </c>
     </row>
   </sheetData>

--- a/tsp_results.xlsx
+++ b/tsp_results.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Raw_Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Statistics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Conclusion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pairwise_Test" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +463,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -480,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,7 +499,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -516,7 +517,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -534,7 +535,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -552,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -570,7 +571,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -588,7 +589,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -606,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -624,7 +625,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>237.7336</v>
+        <v>237.728</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -642,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>201.1148</v>
+        <v>201.0904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -660,11 +661,11 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>192.5553</v>
+        <v>198.3977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -678,11 +679,11 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>203.5522</v>
+        <v>204.9148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -696,11 +697,11 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>198.1805</v>
+        <v>203.1738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -714,11 +715,11 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>198.5912</v>
+        <v>192.5554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -732,11 +733,11 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>204.2231</v>
+        <v>195.9196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -750,11 +751,11 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>192.5553</v>
+        <v>199.3905999999999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -768,11 +769,11 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>215.4902</v>
+        <v>199.2353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -786,11 +787,11 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>192.5553</v>
+        <v>196.4930999999999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -804,11 +805,11 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>206.4804</v>
+        <v>197.6342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -822,11 +823,11 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>260.8398999999999</v>
+        <v>252.6316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -840,11 +841,11 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>224.7089</v>
+        <v>273.8063</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;AEMON Tân Phú-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -858,11 +859,11 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>242.7831</v>
+        <v>255.903</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Chợ Bình Tây-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Sài Gòn Mansion-&gt;KDC Đào Sư Tích-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;UEH Cơ sở B-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -876,11 +877,11 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>283.9088</v>
+        <v>259.8016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;BV Phục hồi chức năng-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -894,11 +895,11 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>227.5023999999999</v>
+        <v>262.25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Bà Chiểu-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;KDC Đào Sư Tích-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;UEH Cơ sở N-&gt;UEH Cơ sở B-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -912,11 +913,11 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>257.1992999999999</v>
+        <v>270.0288</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bình Tây-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Lovera Park Khang Điền-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;AEMON Tân Phú-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở B-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -930,11 +931,11 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>231.7861999999999</v>
+        <v>235.9572999999999</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vincom Plaza Quang Trung-&gt;BV Phục hồi chức năng-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -948,11 +949,11 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>238.1223</v>
+        <v>270.4929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở B-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -966,11 +967,11 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>248.4392999999999</v>
+        <v>277.6381</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu di tích Láng Le Bàu Cò-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Chợ Bình Tây-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;UEH Cơ sở B-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;Chợ Bà Chiểu-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;ĐH Y dược TP.HCM-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;BV Phục hồi chức năng-&gt;Crescent Mall-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -984,11 +985,11 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>287.4814999999999</v>
+        <v>259.4856</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;AEMON Tân Phú-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ Bình Tây-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1002,11 +1003,11 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>206.2975</v>
+        <v>200.8398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1020,11 +1021,11 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>207.4906</v>
+        <v>210.3053</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Bà Chiểu-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1038,11 +1039,11 @@
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>201.0126</v>
+        <v>205.5014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Mitsubishi ISAMCO-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1056,11 +1057,11 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>206.0996</v>
+        <v>204.0442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1074,11 +1075,11 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>207.255</v>
+        <v>198.2917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1092,11 +1093,11 @@
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>202.8928999999999</v>
+        <v>198.9872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1110,11 +1111,11 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>207.6749</v>
+        <v>203.4041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1129,11 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>200.4226</v>
+        <v>204.1196</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1147,11 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>196.3503</v>
+        <v>196.8713</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1164,11 +1165,11 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>198.5151</v>
+        <v>202.9779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,48 +1208,37 @@
           <t>Variance</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2-opt</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>200.52983</v>
+        <v>237.728</v>
       </c>
       <c r="C2" t="n">
-        <v>7.321172730595964</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>53.59957015122197</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.8724377287882789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACO</t>
+          <t>2-opt</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>203.40111</v>
+        <v>198.88049</v>
       </c>
       <c r="C3" t="n">
-        <v>4.135676694447954</v>
+        <v>3.595905</v>
       </c>
       <c r="D3" t="n">
-        <v>17.10382172099996</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.7826092549174236</v>
+        <v>12.930534</v>
       </c>
     </row>
     <row r="4">
@@ -1258,35 +1248,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>250.2771699999999</v>
+        <v>261.79952</v>
       </c>
       <c r="C4" t="n">
-        <v>22.10167948093288</v>
+        <v>12.176974</v>
       </c>
       <c r="D4" t="n">
-        <v>488.4842358778894</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1066776016185869</v>
+        <v>148.278686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>ACO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237.7336</v>
+        <v>202.53425</v>
       </c>
       <c r="C5" t="n">
-        <v>1e-06</v>
+        <v>3.95054</v>
       </c>
       <c r="D5" t="n">
-        <v>1e-12</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.2382754146757105</v>
+        <v>15.606767</v>
       </c>
     </row>
   </sheetData>
@@ -1300,29 +1284,284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Best Algorithm</t>
+          <t>Algo_A</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Algo_B</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mean_A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mean_B</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>t_stat</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Winner</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2-opt</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>237.728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>198.8805</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.1629</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2-opt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>237.728</v>
+      </c>
+      <c r="D3" t="n">
+        <v>261.7995</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-6.2512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ACO</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>237.728</v>
+      </c>
+      <c r="D4" t="n">
+        <v>202.5342</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.1714</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ACO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2-opt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>198.8805</v>
+      </c>
+      <c r="D5" t="n">
+        <v>261.7995</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-15.6707</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2-opt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2-opt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ACO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>198.8805</v>
+      </c>
+      <c r="D6" t="n">
+        <v>202.5342</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.1629</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.022127</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2-opt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ACO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>261.7995</v>
+      </c>
+      <c r="D7" t="n">
+        <v>202.5342</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.6396</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ACO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>2-opt</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8724377287882789</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tsp_results.xlsx
+++ b/tsp_results.xlsx
@@ -661,11 +661,11 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>198.3977</v>
+        <v>191.7122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -679,11 +679,11 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>204.9148</v>
+        <v>203.7957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -697,11 +697,11 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>203.1738</v>
+        <v>198.5913</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -715,11 +715,11 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>192.5554</v>
+        <v>206.0071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -733,11 +733,11 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>195.9196</v>
+        <v>211.544</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>199.3905999999999</v>
+        <v>201.3422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -769,11 +769,11 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>199.2353</v>
+        <v>191.7959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -787,11 +787,11 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>196.4930999999999</v>
+        <v>197.4019</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -805,11 +805,11 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>197.6342</v>
+        <v>210.5302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -823,11 +823,11 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>252.6316</v>
+        <v>280.2713999999999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Lovera Park Khang Điền-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -841,11 +841,11 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>273.8063</v>
+        <v>274.4116999999999</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Sài Gòn Mansion-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sài Gòn Mansion-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -859,11 +859,11 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>255.903</v>
+        <v>267.9772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Sài Gòn Mansion-&gt;KDC Đào Sư Tích-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;UEH Cơ sở B-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;AEMON Tân Phú-&gt;Chợ Bà Chiểu-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;UEH Cơ sở B-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -877,11 +877,11 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>259.8016</v>
+        <v>262.9167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;BV Phục hồi chức năng-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;AEMON Tân Phú-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;UEH Cơ sở B-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;BV Phục hồi chức năng-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -895,11 +895,11 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>262.25</v>
+        <v>242.9999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;KDC Đào Sư Tích-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Bình Tây-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;UEH Cơ sở N-&gt;UEH Cơ sở B-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;AEMON Tân Phú-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Bà Chiểu-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -913,11 +913,11 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>270.0288</v>
+        <v>237.7414999999999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Thảo Điền Pearl-&gt;Mitsubishi ISAMCO-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;AEMON Tân Phú-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở B-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Chợ Bà Chiểu-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;BV Phục hồi chức năng-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Mitsubishi ISAMCO-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -931,11 +931,11 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>235.9572999999999</v>
+        <v>254.7667</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;AEMON Tân Phú-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -949,11 +949,11 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>270.4929</v>
+        <v>257.8953999999999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;UEH Cơ sở B-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -967,11 +967,11 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>277.6381</v>
+        <v>276.7452999999999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Ngã tư Hưng Long-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;ĐH Y dược TP.HCM-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;BV Phục hồi chức năng-&gt;Crescent Mall-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Bà Chiểu-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Lovera Park Khang Điền-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -985,11 +985,11 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>259.4856</v>
+        <v>253.1025999999999</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sài Gòn Mansion-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Sân bay Tân Sơn Nhất-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;AEMON Tân Phú-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1003,11 +1003,11 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>200.8398</v>
+        <v>200.4904999999999</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1021,11 +1021,11 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>210.3053</v>
+        <v>207.3502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1039,11 +1039,11 @@
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>205.5014</v>
+        <v>202.1129</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Mitsubishi ISAMCO-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1057,11 +1057,11 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>204.0442</v>
+        <v>201.5239</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1075,11 +1075,11 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>198.2917</v>
+        <v>202.1672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1093,11 +1093,11 @@
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>198.9872</v>
+        <v>192.9191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1111,11 +1111,11 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>203.4041</v>
+        <v>206.4276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1129,11 +1129,11 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>204.1196</v>
+        <v>207.4908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Bà Chiểu-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1147,11 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>196.8713</v>
+        <v>203.8306</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Sài Gòn Mansion-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Snow Town Sài Gòn-&gt;Thảo Điền Pearl-&gt;Chợ Bà Chiểu-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;Sài Gòn Mansion-&gt;Mitsubishi ISAMCO-&gt;Vạn Phúc City-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1165,11 +1165,11 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>202.9779</v>
+        <v>206.4353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;Crescent Mall-&gt;VINAMILK Tower-&gt;LOTTE Mart Q7-&gt;BV Phục hồi chức năng-&gt;KDC Đào Sư Tích-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;AEMON Tân Phú-&gt;Chợ Vĩnh Lộc A-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Chợ KCN Lê Minh Xuân-&gt;Khu di tích Láng Le Bàu Cò-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Ngã tư Hưng Long-&gt;ĐH Y dược TP.HCM-&gt;Lovera Park Khang Điền-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;UEH Cơ sở N-&gt;Chợ Bình Tây-&gt;UEH Cơ sở B-&gt;Sài Gòn Mansion-&gt;Sân bay Tân Sơn Nhất-&gt;Vincom Plaza Quang Trung-&gt;Chợ Thạch Đà-&gt;Khu dân cư bảo phú</t>
+          <t>Khu dân cư bảo phú-&gt;Vạn Phúc City-&gt;Mitsubishi ISAMCO-&gt;Chợ Bà Chiểu-&gt;Sài Gòn Mansion-&gt;UEH Cơ sở B-&gt;Chợ Bình Tây-&gt;UEH Cơ sở N-&gt;Cơ Khí Bao Bì Quốc Cường-&gt;Lovera Park Khang Điền-&gt;ĐH Y dược TP.HCM-&gt;Ngã tư Hưng Long-&gt;Bệnh viện Nhi Đồng Thành Phố-&gt;Khu di tích Láng Le Bàu Cò-&gt;Chợ KCN Lê Minh Xuân-&gt;Bệnh Viện Đa Khoa Quốc Ánh-&gt;Trạm Y Tế Xã Bình Lợi-&gt;Hồ Câu Giải Trí Đồng Bưng-&gt;Chợ Vĩnh Lộc A-&gt;AEMON Tân Phú-&gt;Chợ Thạch Đà-&gt;Vincom Plaza Quang Trung-&gt;Sân bay Tân Sơn Nhất-&gt;Thảo Điền Pearl-&gt;Snow Town Sài Gòn-&gt;VINAMILK Tower-&gt;Crescent Mall-&gt;KDC Đào Sư Tích-&gt;BV Phục hồi chức năng-&gt;LOTTE Mart Q7-&gt;Khu dân cư bảo phú</t>
         </is>
       </c>
     </row>
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>198.88049</v>
+        <v>201.38109</v>
       </c>
       <c r="C3" t="n">
-        <v>3.595905</v>
+        <v>6.857984</v>
       </c>
       <c r="D3" t="n">
-        <v>12.930534</v>
+        <v>47.03194</v>
       </c>
     </row>
     <row r="4">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>261.79952</v>
+        <v>260.88284</v>
       </c>
       <c r="C4" t="n">
-        <v>12.176974</v>
+        <v>14.248648</v>
       </c>
       <c r="D4" t="n">
-        <v>148.278686</v>
+        <v>203.023971</v>
       </c>
     </row>
     <row r="5">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>202.53425</v>
+        <v>203.07481</v>
       </c>
       <c r="C5" t="n">
-        <v>3.95054</v>
+        <v>4.40778</v>
       </c>
       <c r="D5" t="n">
-        <v>15.606767</v>
+        <v>19.428521</v>
       </c>
     </row>
   </sheetData>
@@ -1339,10 +1339,10 @@
         <v>237.728</v>
       </c>
       <c r="D2" t="n">
-        <v>198.8805</v>
+        <v>201.3811</v>
       </c>
       <c r="E2" t="n">
-        <v>34.1629</v>
+        <v>16.7599</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1368,13 +1368,13 @@
         <v>237.728</v>
       </c>
       <c r="D3" t="n">
-        <v>261.7995</v>
+        <v>260.8828</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.2512</v>
+        <v>-5.1389</v>
       </c>
       <c r="F3" t="n">
-        <v>3e-06</v>
+        <v>3.4e-05</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         <v>237.728</v>
       </c>
       <c r="D4" t="n">
-        <v>202.5342</v>
+        <v>203.0748</v>
       </c>
       <c r="E4" t="n">
-        <v>28.1714</v>
+        <v>24.8613</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>198.8805</v>
+        <v>201.3811</v>
       </c>
       <c r="D5" t="n">
-        <v>261.7995</v>
+        <v>260.8828</v>
       </c>
       <c r="E5" t="n">
-        <v>-15.6707</v>
+        <v>-11.899</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1452,20 +1452,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>198.8805</v>
+        <v>201.3811</v>
       </c>
       <c r="D6" t="n">
-        <v>202.5342</v>
+        <v>203.0748</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1629</v>
+        <v>-0.657</v>
       </c>
       <c r="F6" t="n">
-        <v>0.022127</v>
+        <v>0.259749</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2-opt</t>
+          <t>Không đủ bằng chứng</t>
         </is>
       </c>
     </row>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>261.7995</v>
+        <v>260.8828</v>
       </c>
       <c r="D7" t="n">
-        <v>202.5342</v>
+        <v>203.0748</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6396</v>
+        <v>12.2566</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
